--- a/Access Master.xlsx
+++ b/Access Master.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Harshal Thakkar\Dashboard\Sales &amp; Installation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Harshal Thakkar\Dashboard\Sales &amp; Installation\sales-dashboard-rbac\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -41,9 +41,6 @@
     <t>Region/City</t>
   </si>
   <si>
-    <t>TP001</t>
-  </si>
-  <si>
     <t>manager1</t>
   </si>
   <si>
@@ -56,45 +53,30 @@
     <t>ALL</t>
   </si>
   <si>
-    <t>SM001</t>
-  </si>
-  <si>
     <t>manager2</t>
   </si>
   <si>
     <t>SMA_9999</t>
   </si>
   <si>
-    <t>HT001</t>
-  </si>
-  <si>
     <t>manager3</t>
   </si>
   <si>
     <t>H@rt2677</t>
   </si>
   <si>
-    <t>SN001</t>
-  </si>
-  <si>
     <t>manager4</t>
   </si>
   <si>
     <t>SNA_9978</t>
   </si>
   <si>
-    <t>GP001</t>
-  </si>
-  <si>
     <t>manager5</t>
   </si>
   <si>
     <t>GPA_5689</t>
   </si>
   <si>
-    <t>RB001</t>
-  </si>
-  <si>
     <t>lead1</t>
   </si>
   <si>
@@ -107,9 +89,6 @@
     <t>VADODARA,AHMEDABAD</t>
   </si>
   <si>
-    <t>SM002</t>
-  </si>
-  <si>
     <t>lead2</t>
   </si>
   <si>
@@ -119,9 +98,6 @@
     <t>PUNE,MUMBAI,CHENNAI,NAGPUR,BANGALORE,VISHAKAPATNAM,HYDERABAD,KAKINADA,VIJAYAWADA,AURANGABAD,NASHIK</t>
   </si>
   <si>
-    <t>AA001</t>
-  </si>
-  <si>
     <t>lead3</t>
   </si>
   <si>
@@ -129,6 +105,30 @@
   </si>
   <si>
     <t>RAJKOT</t>
+  </si>
+  <si>
+    <t>Tarpan Patel</t>
+  </si>
+  <si>
+    <t>Sameer Mahapatra</t>
+  </si>
+  <si>
+    <t>Harshal Thakkar</t>
+  </si>
+  <si>
+    <t>Sunish Nair</t>
+  </si>
+  <si>
+    <t>Gaurang Patel</t>
+  </si>
+  <si>
+    <t>Rajiv Bhatiya</t>
+  </si>
+  <si>
+    <t>Srinivas Mallavelli</t>
+  </si>
+  <si>
+    <t>Animesh Agarwal</t>
   </si>
 </sst>
 </file>
@@ -448,6 +448,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -468,138 +471,138 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
       <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
         <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
         <v>8</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
         <v>8</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" t="s">
         <v>8</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Access Master.xlsx
+++ b/Access Master.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="39">
   <si>
     <t>UserID</t>
   </si>
@@ -129,6 +129,18 @@
   </si>
   <si>
     <t>Animesh Agarwal</t>
+  </si>
+  <si>
+    <t>Hitesh Gandhi</t>
+  </si>
+  <si>
+    <t>manager6</t>
+  </si>
+  <si>
+    <t>HGM_555</t>
+  </si>
+  <si>
+    <t>All</t>
   </si>
 </sst>
 </file>
@@ -446,10 +458,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -605,6 +618,23 @@
         <v>26</v>
       </c>
     </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Access Master.xlsx
+++ b/Access Master.xlsx
@@ -44,9 +44,6 @@
     <t>manager1</t>
   </si>
   <si>
-    <t>TPAG_789</t>
-  </si>
-  <si>
     <t>Manager</t>
   </si>
   <si>
@@ -80,9 +77,6 @@
     <t>lead1</t>
   </si>
   <si>
-    <t>RB_VA7389</t>
-  </si>
-  <si>
     <t>Regional Lead</t>
   </si>
   <si>
@@ -92,9 +86,6 @@
     <t>lead2</t>
   </si>
   <si>
-    <t>SMSM_8349</t>
-  </si>
-  <si>
     <t>PUNE,MUMBAI,CHENNAI,NAGPUR,BANGALORE,VISHAKAPATNAM,HYDERABAD,KAKINADA,VIJAYAWADA,AURANGABAD,NASHIK</t>
   </si>
   <si>
@@ -141,6 +132,15 @@
   </si>
   <si>
     <t>All</t>
+  </si>
+  <si>
+    <t>TPAP_789</t>
+  </si>
+  <si>
+    <t>RKB_VA7389</t>
+  </si>
+  <si>
+    <t>SMSMV_8349</t>
   </si>
 </sst>
 </file>
@@ -463,6 +463,9 @@
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="116.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -484,155 +487,155 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
       </c>
       <c r="C2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
       <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" t="s">
         <v>7</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
       <c r="D4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" t="s">
         <v>7</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
       <c r="D5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" t="s">
         <v>7</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
       <c r="D6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" t="s">
         <v>7</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>18</v>
-      </c>
-      <c r="D7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" t="s">
         <v>35</v>
-      </c>
-      <c r="B10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/Access Master.xlsx
+++ b/Access Master.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="42">
   <si>
     <t>UserID</t>
   </si>
@@ -41,57 +41,30 @@
     <t>Region/City</t>
   </si>
   <si>
-    <t>manager1</t>
-  </si>
-  <si>
     <t>Manager</t>
   </si>
   <si>
     <t>ALL</t>
   </si>
   <si>
-    <t>manager2</t>
-  </si>
-  <si>
     <t>SMA_9999</t>
   </si>
   <si>
-    <t>manager3</t>
-  </si>
-  <si>
     <t>H@rt2677</t>
   </si>
   <si>
-    <t>manager4</t>
-  </si>
-  <si>
     <t>SNA_9978</t>
   </si>
   <si>
-    <t>manager5</t>
-  </si>
-  <si>
     <t>GPA_5689</t>
   </si>
   <si>
-    <t>lead1</t>
-  </si>
-  <si>
     <t>Regional Lead</t>
   </si>
   <si>
     <t>VADODARA,AHMEDABAD</t>
   </si>
   <si>
-    <t>lead2</t>
-  </si>
-  <si>
-    <t>PUNE,MUMBAI,CHENNAI,NAGPUR,BANGALORE,VISHAKAPATNAM,HYDERABAD,KAKINADA,VIJAYAWADA,AURANGABAD,NASHIK</t>
-  </si>
-  <si>
-    <t>lead3</t>
-  </si>
-  <si>
     <t>AAR_6943</t>
   </si>
   <si>
@@ -125,9 +98,6 @@
     <t>Hitesh Gandhi</t>
   </si>
   <si>
-    <t>manager6</t>
-  </si>
-  <si>
     <t>HGM_555</t>
   </si>
   <si>
@@ -141,6 +111,45 @@
   </si>
   <si>
     <t>SMSMV_8349</t>
+  </si>
+  <si>
+    <t>tpatel</t>
+  </si>
+  <si>
+    <t>smahapatra</t>
+  </si>
+  <si>
+    <t>hthakkar</t>
+  </si>
+  <si>
+    <t>snair</t>
+  </si>
+  <si>
+    <t>gpatel</t>
+  </si>
+  <si>
+    <t>rbhatiya</t>
+  </si>
+  <si>
+    <t>smallavelli</t>
+  </si>
+  <si>
+    <t>agarwal</t>
+  </si>
+  <si>
+    <t>hgandhi</t>
+  </si>
+  <si>
+    <t>Chandresh Fanawala</t>
+  </si>
+  <si>
+    <t>cfanawala</t>
+  </si>
+  <si>
+    <t>CFA_6589</t>
+  </si>
+  <si>
+    <t>PUNE,MUMBAI,NAGPUR,VISHAKAPATNAM,AURANGABAD,NASHIK</t>
   </si>
 </sst>
 </file>
@@ -458,11 +467,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="116.7109375" bestFit="1" customWidth="1"/>
@@ -487,155 +496,172 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
         <v>6</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
         <v>6</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s">
         <v>6</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
         <v>6</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Access Master.xlsx
+++ b/Access Master.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="53">
   <si>
     <t>UserID</t>
   </si>
@@ -41,125 +41,165 @@
     <t>Region/City</t>
   </si>
   <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>SMA_9999</t>
+  </si>
+  <si>
+    <t>H@rt2677</t>
+  </si>
+  <si>
+    <t>SNA_9978</t>
+  </si>
+  <si>
+    <t>GPA_5689</t>
+  </si>
+  <si>
+    <t>VADODARA,AHMEDABAD</t>
+  </si>
+  <si>
+    <t>AAR_6943</t>
+  </si>
+  <si>
+    <t>RAJKOT</t>
+  </si>
+  <si>
+    <t>Tarpan Patel</t>
+  </si>
+  <si>
+    <t>Sameer Mahapatra</t>
+  </si>
+  <si>
+    <t>Harshal Thakkar</t>
+  </si>
+  <si>
+    <t>Sunish Nair</t>
+  </si>
+  <si>
+    <t>Gaurang Patel</t>
+  </si>
+  <si>
+    <t>Rajiv Bhatiya</t>
+  </si>
+  <si>
+    <t>Srinivas Mallavelli</t>
+  </si>
+  <si>
+    <t>Animesh Agarwal</t>
+  </si>
+  <si>
+    <t>Hitesh Gandhi</t>
+  </si>
+  <si>
+    <t>HGM_555</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>TPAP_789</t>
+  </si>
+  <si>
+    <t>RKB_VA7389</t>
+  </si>
+  <si>
+    <t>SMSMV_8349</t>
+  </si>
+  <si>
+    <t>tpatel</t>
+  </si>
+  <si>
+    <t>smahapatra</t>
+  </si>
+  <si>
+    <t>hthakkar</t>
+  </si>
+  <si>
+    <t>snair</t>
+  </si>
+  <si>
+    <t>gpatel</t>
+  </si>
+  <si>
+    <t>rbhatiya</t>
+  </si>
+  <si>
+    <t>smallavelli</t>
+  </si>
+  <si>
+    <t>agarwal</t>
+  </si>
+  <si>
+    <t>hgandhi</t>
+  </si>
+  <si>
+    <t>Chandresh Fanawala</t>
+  </si>
+  <si>
+    <t>cfanawala</t>
+  </si>
+  <si>
+    <t>CFA_6589</t>
+  </si>
+  <si>
+    <t>PUNE,MUMBAI,NAGPUR,VISHAKAPATNAM,AURANGABAD,NASHIK</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>tarpan.patel@youbroadband.co.in</t>
+  </si>
+  <si>
+    <t>rajivkumar.bhatiya@youbroadband.co.in</t>
+  </si>
+  <si>
+    <t>harshal.thakkar@youbroadband.co.in</t>
+  </si>
+  <si>
+    <t>srinivas.mallavelli@youbroadband.co.in</t>
+  </si>
+  <si>
+    <t>animesh.agarwal@youbroadband.co.in</t>
+  </si>
+  <si>
+    <t>hitesh.gandhi@youbroadband.co.in</t>
+  </si>
+  <si>
+    <t>chandresh.fanawala@youbroadband.co.in</t>
+  </si>
+  <si>
+    <t>gaurangkumar.patel1@youbroadband.co.in</t>
+  </si>
+  <si>
+    <t>sunish.nair1@youbroadband.co.in</t>
+  </si>
+  <si>
+    <t>sameer.mahapatra@youbroadband.co.in</t>
+  </si>
+  <si>
     <t>Manager</t>
   </si>
   <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>SMA_9999</t>
-  </si>
-  <si>
-    <t>H@rt2677</t>
-  </si>
-  <si>
-    <t>SNA_9978</t>
-  </si>
-  <si>
-    <t>GPA_5689</t>
-  </si>
-  <si>
     <t>Regional Lead</t>
-  </si>
-  <si>
-    <t>VADODARA,AHMEDABAD</t>
-  </si>
-  <si>
-    <t>AAR_6943</t>
-  </si>
-  <si>
-    <t>RAJKOT</t>
-  </si>
-  <si>
-    <t>Tarpan Patel</t>
-  </si>
-  <si>
-    <t>Sameer Mahapatra</t>
-  </si>
-  <si>
-    <t>Harshal Thakkar</t>
-  </si>
-  <si>
-    <t>Sunish Nair</t>
-  </si>
-  <si>
-    <t>Gaurang Patel</t>
-  </si>
-  <si>
-    <t>Rajiv Bhatiya</t>
-  </si>
-  <si>
-    <t>Srinivas Mallavelli</t>
-  </si>
-  <si>
-    <t>Animesh Agarwal</t>
-  </si>
-  <si>
-    <t>Hitesh Gandhi</t>
-  </si>
-  <si>
-    <t>HGM_555</t>
-  </si>
-  <si>
-    <t>All</t>
-  </si>
-  <si>
-    <t>TPAP_789</t>
-  </si>
-  <si>
-    <t>RKB_VA7389</t>
-  </si>
-  <si>
-    <t>SMSMV_8349</t>
-  </si>
-  <si>
-    <t>tpatel</t>
-  </si>
-  <si>
-    <t>smahapatra</t>
-  </si>
-  <si>
-    <t>hthakkar</t>
-  </si>
-  <si>
-    <t>snair</t>
-  </si>
-  <si>
-    <t>gpatel</t>
-  </si>
-  <si>
-    <t>rbhatiya</t>
-  </si>
-  <si>
-    <t>smallavelli</t>
-  </si>
-  <si>
-    <t>agarwal</t>
-  </si>
-  <si>
-    <t>hgandhi</t>
-  </si>
-  <si>
-    <t>Chandresh Fanawala</t>
-  </si>
-  <si>
-    <t>cfanawala</t>
-  </si>
-  <si>
-    <t>CFA_6589</t>
-  </si>
-  <si>
-    <t>PUNE,MUMBAI,NAGPUR,VISHAKAPATNAM,AURANGABAD,NASHIK</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0D001A"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -185,8 +225,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -467,204 +509,239 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="116.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="116.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="D8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="C9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E7" t="s">
+      <c r="D9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="C10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B9" t="s">
+      <c r="D10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="B10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Access Master.xlsx
+++ b/Access Master.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="59">
   <si>
     <t>UserID</t>
   </si>
@@ -179,10 +179,28 @@
     <t>sameer.mahapatra@youbroadband.co.in</t>
   </si>
   <si>
-    <t>Manager</t>
-  </si>
-  <si>
     <t>Regional Lead</t>
+  </si>
+  <si>
+    <t>Manager1</t>
+  </si>
+  <si>
+    <t>Manager2</t>
+  </si>
+  <si>
+    <t>Manager3</t>
+  </si>
+  <si>
+    <t>Manager4</t>
+  </si>
+  <si>
+    <t>Manager5</t>
+  </si>
+  <si>
+    <t>Manager6</t>
+  </si>
+  <si>
+    <t>Manager7</t>
   </si>
 </sst>
 </file>
@@ -551,7 +569,7 @@
         <v>24</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>41</v>
@@ -571,7 +589,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>50</v>
@@ -591,7 +609,7 @@
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>43</v>
@@ -611,7 +629,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>49</v>
@@ -631,7 +649,7 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>48</v>
@@ -651,7 +669,7 @@
         <v>25</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>42</v>
@@ -671,7 +689,7 @@
         <v>26</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>44</v>
@@ -691,7 +709,7 @@
         <v>11</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>45</v>
@@ -711,7 +729,7 @@
         <v>22</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>46</v>
@@ -731,7 +749,7 @@
         <v>38</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>47</v>

--- a/Access Master.xlsx
+++ b/Access Master.xlsx
@@ -47,21 +47,9 @@
     <t>SMA_9999</t>
   </si>
   <si>
-    <t>H@rt2677</t>
-  </si>
-  <si>
-    <t>SNA_9978</t>
-  </si>
-  <si>
-    <t>GPA_5689</t>
-  </si>
-  <si>
     <t>VADODARA,AHMEDABAD</t>
   </si>
   <si>
-    <t>AAR_6943</t>
-  </si>
-  <si>
     <t>RAJKOT</t>
   </si>
   <si>
@@ -92,21 +80,12 @@
     <t>Hitesh Gandhi</t>
   </si>
   <si>
-    <t>HGM_555</t>
-  </si>
-  <si>
     <t>All</t>
   </si>
   <si>
     <t>TPAP_789</t>
   </si>
   <si>
-    <t>RKB_VA7389</t>
-  </si>
-  <si>
-    <t>SMSMV_8349</t>
-  </si>
-  <si>
     <t>tpatel</t>
   </si>
   <si>
@@ -140,9 +119,6 @@
     <t>cfanawala</t>
   </si>
   <si>
-    <t>CFA_6589</t>
-  </si>
-  <si>
     <t>PUNE,MUMBAI,NAGPUR,VISHAKAPATNAM,AURANGABAD,NASHIK</t>
   </si>
   <si>
@@ -201,6 +177,30 @@
   </si>
   <si>
     <t>Manager7</t>
+  </si>
+  <si>
+    <t>SNA_9979</t>
+  </si>
+  <si>
+    <t>GPA_5688</t>
+  </si>
+  <si>
+    <t>RKB_VA7387</t>
+  </si>
+  <si>
+    <t>SMSMV_8347</t>
+  </si>
+  <si>
+    <t>AAR_6944</t>
+  </si>
+  <si>
+    <t>HGM_556</t>
+  </si>
+  <si>
+    <t>CFA_6584</t>
+  </si>
+  <si>
+    <t>H@rt2905</t>
   </si>
 </sst>
 </file>
@@ -552,7 +552,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -560,19 +560,19 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>5</v>
@@ -580,19 +580,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>5</v>
@@ -600,19 +600,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>7</v>
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>58</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>5</v>
@@ -620,19 +620,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>5</v>
@@ -640,19 +640,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>5</v>
@@ -660,102 +660,102 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Access Master.xlsx
+++ b/Access Master.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="53">
   <si>
     <t>UserID</t>
   </si>
@@ -158,27 +158,6 @@
     <t>Regional Lead</t>
   </si>
   <si>
-    <t>Manager1</t>
-  </si>
-  <si>
-    <t>Manager2</t>
-  </si>
-  <si>
-    <t>Manager3</t>
-  </si>
-  <si>
-    <t>Manager4</t>
-  </si>
-  <si>
-    <t>Manager5</t>
-  </si>
-  <si>
-    <t>Manager6</t>
-  </si>
-  <si>
-    <t>Manager7</t>
-  </si>
-  <si>
     <t>SNA_9979</t>
   </si>
   <si>
@@ -201,6 +180,9 @@
   </si>
   <si>
     <t>H@rt2905</t>
+  </si>
+  <si>
+    <t>Manager</t>
   </si>
 </sst>
 </file>
@@ -569,7 +551,7 @@
         <v>19</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>33</v>
@@ -589,7 +571,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>42</v>
@@ -606,10 +588,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>35</v>
@@ -626,10 +608,10 @@
         <v>23</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>41</v>
@@ -646,10 +628,10 @@
         <v>24</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>40</v>
@@ -666,7 +648,7 @@
         <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>43</v>
@@ -686,7 +668,7 @@
         <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>43</v>
@@ -706,7 +688,7 @@
         <v>27</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>43</v>
@@ -726,10 +708,10 @@
         <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>38</v>
@@ -746,10 +728,10 @@
         <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>39</v>

--- a/Access Master.xlsx
+++ b/Access Master.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Harshal Thakkar\Dashboard\Sales &amp; Installation\sales-dashboard-rbac\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Harshal Thakkar\Dashboard\Sales &amp; Installation\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="63">
   <si>
     <t>UserID</t>
   </si>
@@ -44,145 +44,175 @@
     <t>ALL</t>
   </si>
   <si>
+    <t>Harshal Thakkar</t>
+  </si>
+  <si>
+    <t>hthakkar</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>harshal.thakkar@youbroadband.co.in</t>
+  </si>
+  <si>
+    <t>H@rt2905</t>
+  </si>
+  <si>
+    <t>Manager</t>
+  </si>
+  <si>
+    <t>Designation</t>
+  </si>
+  <si>
+    <t>Sr. VP Marketing &amp; Customer Retention</t>
+  </si>
+  <si>
+    <t>Tarpan Patel</t>
+  </si>
+  <si>
+    <t>tpatel</t>
+  </si>
+  <si>
+    <t>TPAP_789</t>
+  </si>
+  <si>
+    <t>tarpan.patel@youbroadband.co.in</t>
+  </si>
+  <si>
+    <t>Sameer Mahapatra</t>
+  </si>
+  <si>
+    <t>smahapatra</t>
+  </si>
+  <si>
     <t>SMA_9999</t>
   </si>
   <si>
+    <t>sameer.mahapatra@youbroadband.co.in</t>
+  </si>
+  <si>
+    <t>Sunish Nair</t>
+  </si>
+  <si>
+    <t>snair</t>
+  </si>
+  <si>
+    <t>SNA_9979</t>
+  </si>
+  <si>
+    <t>sunish.nair1@youbroadband.co.in</t>
+  </si>
+  <si>
+    <t>Gaurang Patel</t>
+  </si>
+  <si>
+    <t>gpatel</t>
+  </si>
+  <si>
+    <t>GPA_5688</t>
+  </si>
+  <si>
+    <t>gaurangkumar.patel1@youbroadband.co.in</t>
+  </si>
+  <si>
+    <t>Rajiv Bhatiya</t>
+  </si>
+  <si>
+    <t>rbhatiya</t>
+  </si>
+  <si>
+    <t>RKB_VA7387</t>
+  </si>
+  <si>
+    <t>Regional Lead</t>
+  </si>
+  <si>
+    <t>rajivkumar.bhatiya@youbroadband.co.in</t>
+  </si>
+  <si>
     <t>VADODARA,AHMEDABAD</t>
   </si>
   <si>
+    <t>Srinivas Mallavelli</t>
+  </si>
+  <si>
+    <t>smallavelli</t>
+  </si>
+  <si>
+    <t>SMSMV_8347</t>
+  </si>
+  <si>
+    <t>srinivas.mallavelli@youbroadband.co.in</t>
+  </si>
+  <si>
+    <t>PUNE,MUMBAI,NAGPUR,VISHAKAPATNAM,AURANGABAD,NASHIK</t>
+  </si>
+  <si>
+    <t>Animesh Agarwal</t>
+  </si>
+  <si>
+    <t>agarwal</t>
+  </si>
+  <si>
+    <t>AAR_6944</t>
+  </si>
+  <si>
+    <t>animesh.agarwal@youbroadband.co.in</t>
+  </si>
+  <si>
     <t>RAJKOT</t>
   </si>
   <si>
-    <t>Tarpan Patel</t>
-  </si>
-  <si>
-    <t>Sameer Mahapatra</t>
-  </si>
-  <si>
-    <t>Harshal Thakkar</t>
-  </si>
-  <si>
-    <t>Sunish Nair</t>
-  </si>
-  <si>
-    <t>Gaurang Patel</t>
-  </si>
-  <si>
-    <t>Rajiv Bhatiya</t>
-  </si>
-  <si>
-    <t>Srinivas Mallavelli</t>
-  </si>
-  <si>
-    <t>Animesh Agarwal</t>
-  </si>
-  <si>
     <t>Hitesh Gandhi</t>
   </si>
   <si>
+    <t>hgandhi</t>
+  </si>
+  <si>
+    <t>hitesh.gandhi@youbroadband.co.in</t>
+  </si>
+  <si>
     <t>All</t>
   </si>
   <si>
-    <t>TPAP_789</t>
-  </si>
-  <si>
-    <t>tpatel</t>
-  </si>
-  <si>
-    <t>smahapatra</t>
-  </si>
-  <si>
-    <t>hthakkar</t>
-  </si>
-  <si>
-    <t>snair</t>
-  </si>
-  <si>
-    <t>gpatel</t>
-  </si>
-  <si>
-    <t>rbhatiya</t>
-  </si>
-  <si>
-    <t>smallavelli</t>
-  </si>
-  <si>
-    <t>agarwal</t>
-  </si>
-  <si>
-    <t>hgandhi</t>
-  </si>
-  <si>
     <t>Chandresh Fanawala</t>
   </si>
   <si>
     <t>cfanawala</t>
   </si>
   <si>
-    <t>PUNE,MUMBAI,NAGPUR,VISHAKAPATNAM,AURANGABAD,NASHIK</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>tarpan.patel@youbroadband.co.in</t>
-  </si>
-  <si>
-    <t>rajivkumar.bhatiya@youbroadband.co.in</t>
-  </si>
-  <si>
-    <t>harshal.thakkar@youbroadband.co.in</t>
-  </si>
-  <si>
-    <t>srinivas.mallavelli@youbroadband.co.in</t>
-  </si>
-  <si>
-    <t>animesh.agarwal@youbroadband.co.in</t>
-  </si>
-  <si>
-    <t>hitesh.gandhi@youbroadband.co.in</t>
+    <t>CFA_6584</t>
   </si>
   <si>
     <t>chandresh.fanawala@youbroadband.co.in</t>
   </si>
   <si>
-    <t>gaurangkumar.patel1@youbroadband.co.in</t>
-  </si>
-  <si>
-    <t>sunish.nair1@youbroadband.co.in</t>
-  </si>
-  <si>
-    <t>sameer.mahapatra@youbroadband.co.in</t>
-  </si>
-  <si>
-    <t>Regional Lead</t>
-  </si>
-  <si>
-    <t>SNA_9979</t>
-  </si>
-  <si>
-    <t>GPA_5688</t>
-  </si>
-  <si>
-    <t>RKB_VA7387</t>
-  </si>
-  <si>
-    <t>SMSMV_8347</t>
-  </si>
-  <si>
-    <t>AAR_6944</t>
-  </si>
-  <si>
-    <t>HGM_556</t>
-  </si>
-  <si>
-    <t>CFA_6584</t>
-  </si>
-  <si>
-    <t>H@rt2905</t>
-  </si>
-  <si>
-    <t>Manager</t>
+    <t>CEO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retention Head </t>
+  </si>
+  <si>
+    <t>VP - National  Retail Sales Head</t>
+  </si>
+  <si>
+    <t>VP - Head Finance  &amp; Accounts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGM - Retention Head </t>
+  </si>
+  <si>
+    <t>Manager Business Analyst &amp; MIS</t>
+  </si>
+  <si>
+    <t>GM - Regional Sales Head</t>
+  </si>
+  <si>
+    <t>Regional Sales Head</t>
+  </si>
+  <si>
+    <t>HGM_555</t>
   </si>
 </sst>
 </file>
@@ -213,7 +243,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -221,14 +251,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -509,18 +558,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="116.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -534,210 +584,243 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>52</v>
+        <v>16</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>52</v>
+        <v>28</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>43</v>
+        <v>32</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="G10" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>52</v>
+      <c r="D11" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>18</v>
+        <v>49</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/Access Master.xlsx
+++ b/Access Master.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>UserID</t>
   </si>
@@ -66,153 +66,6 @@
   </si>
   <si>
     <t>Sr. VP Marketing &amp; Customer Retention</t>
-  </si>
-  <si>
-    <t>Tarpan Patel</t>
-  </si>
-  <si>
-    <t>tpatel</t>
-  </si>
-  <si>
-    <t>TPAP_789</t>
-  </si>
-  <si>
-    <t>tarpan.patel@youbroadband.co.in</t>
-  </si>
-  <si>
-    <t>Sameer Mahapatra</t>
-  </si>
-  <si>
-    <t>smahapatra</t>
-  </si>
-  <si>
-    <t>SMA_9999</t>
-  </si>
-  <si>
-    <t>sameer.mahapatra@youbroadband.co.in</t>
-  </si>
-  <si>
-    <t>Sunish Nair</t>
-  </si>
-  <si>
-    <t>snair</t>
-  </si>
-  <si>
-    <t>SNA_9979</t>
-  </si>
-  <si>
-    <t>sunish.nair1@youbroadband.co.in</t>
-  </si>
-  <si>
-    <t>Gaurang Patel</t>
-  </si>
-  <si>
-    <t>gpatel</t>
-  </si>
-  <si>
-    <t>GPA_5688</t>
-  </si>
-  <si>
-    <t>gaurangkumar.patel1@youbroadband.co.in</t>
-  </si>
-  <si>
-    <t>Rajiv Bhatiya</t>
-  </si>
-  <si>
-    <t>rbhatiya</t>
-  </si>
-  <si>
-    <t>RKB_VA7387</t>
-  </si>
-  <si>
-    <t>Regional Lead</t>
-  </si>
-  <si>
-    <t>rajivkumar.bhatiya@youbroadband.co.in</t>
-  </si>
-  <si>
-    <t>VADODARA,AHMEDABAD</t>
-  </si>
-  <si>
-    <t>Srinivas Mallavelli</t>
-  </si>
-  <si>
-    <t>smallavelli</t>
-  </si>
-  <si>
-    <t>SMSMV_8347</t>
-  </si>
-  <si>
-    <t>srinivas.mallavelli@youbroadband.co.in</t>
-  </si>
-  <si>
-    <t>PUNE,MUMBAI,NAGPUR,VISHAKAPATNAM,AURANGABAD,NASHIK</t>
-  </si>
-  <si>
-    <t>Animesh Agarwal</t>
-  </si>
-  <si>
-    <t>agarwal</t>
-  </si>
-  <si>
-    <t>AAR_6944</t>
-  </si>
-  <si>
-    <t>animesh.agarwal@youbroadband.co.in</t>
-  </si>
-  <si>
-    <t>RAJKOT</t>
-  </si>
-  <si>
-    <t>Hitesh Gandhi</t>
-  </si>
-  <si>
-    <t>hgandhi</t>
-  </si>
-  <si>
-    <t>hitesh.gandhi@youbroadband.co.in</t>
-  </si>
-  <si>
-    <t>All</t>
-  </si>
-  <si>
-    <t>Chandresh Fanawala</t>
-  </si>
-  <si>
-    <t>cfanawala</t>
-  </si>
-  <si>
-    <t>CFA_6584</t>
-  </si>
-  <si>
-    <t>chandresh.fanawala@youbroadband.co.in</t>
-  </si>
-  <si>
-    <t>CEO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retention Head </t>
-  </si>
-  <si>
-    <t>VP - National  Retail Sales Head</t>
-  </si>
-  <si>
-    <t>VP - Head Finance  &amp; Accounts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGM - Retention Head </t>
-  </si>
-  <si>
-    <t>Manager Business Analyst &amp; MIS</t>
-  </si>
-  <si>
-    <t>GM - Regional Sales Head</t>
-  </si>
-  <si>
-    <t>Regional Sales Head</t>
-  </si>
-  <si>
-    <t>HGM_555</t>
   </si>
 </sst>
 </file>
@@ -270,14 +123,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -558,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
@@ -603,7 +452,7 @@
       <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -614,213 +463,6 @@
       </c>
       <c r="G2" s="1" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
